--- a/portfolio_eak_analysis_report.xlsx
+++ b/portfolio_eak_analysis_report.xlsx
@@ -478,10 +478,10 @@
         <v>10.52</v>
       </c>
       <c r="D2" t="n">
-        <v>9.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.220532319391625</v>
+        <v>-12.0722433460076</v>
       </c>
       <c r="F2" t="n">
         <v>58</v>
@@ -505,10 +505,10 @@
         <v>13.02</v>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>70.50691244239631</v>
+        <v>68.97081413210446</v>
       </c>
       <c r="F3" t="n">
         <v>68</v>
@@ -532,10 +532,10 @@
         <v>4.65</v>
       </c>
       <c r="D4" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="E4" t="n">
-        <v>-16.55913978494624</v>
+        <v>-16.98924731182797</v>
       </c>
       <c r="F4" t="n">
         <v>60</v>
@@ -559,10 +559,10 @@
         <v>4.83</v>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="E5" t="n">
-        <v>198.1366459627329</v>
+        <v>200.2070393374741</v>
       </c>
       <c r="F5" t="n">
         <v>18</v>
@@ -613,10 +613,10 @@
         <v>14.52</v>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>36.5</v>
       </c>
       <c r="E7" t="n">
-        <v>168.5950413223141</v>
+        <v>151.3774104683196</v>
       </c>
       <c r="F7" t="n">
         <v>32</v>
@@ -667,10 +667,10 @@
         <v>16.19</v>
       </c>
       <c r="D9" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="E9" t="n">
-        <v>-55.52810376775788</v>
+        <v>-54.91043854231007</v>
       </c>
       <c r="F9" t="n">
         <v>54</v>
@@ -694,10 +694,10 @@
         <v>27.32</v>
       </c>
       <c r="D10" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="E10" t="n">
-        <v>-44.72913616398243</v>
+        <v>-45.46120058565153</v>
       </c>
       <c r="F10" t="n">
         <v>68</v>
@@ -721,10 +721,10 @@
         <v>38.94</v>
       </c>
       <c r="D11" t="n">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="n">
-        <v>-66.87211093990754</v>
+        <v>-64.30405752439651</v>
       </c>
       <c r="F11" t="n">
         <v>74</v>
@@ -748,10 +748,10 @@
         <v>12.39</v>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.41162227602906</v>
+        <v>-9.60451977401131</v>
       </c>
       <c r="F12" t="n">
         <v>52</v>
@@ -796,10 +796,10 @@
         <v>5.51</v>
       </c>
       <c r="D14" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>43.37568058076226</v>
+        <v>45.19056261343014</v>
       </c>
       <c r="F14" t="n">
         <v>74</v>
@@ -823,10 +823,10 @@
         <v>23.27</v>
       </c>
       <c r="D15" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="E15" t="n">
-        <v>-51.86935969058874</v>
+        <v>-53.58831113021056</v>
       </c>
       <c r="F15" t="n">
         <v>54</v>
@@ -850,10 +850,10 @@
         <v>3.81</v>
       </c>
       <c r="D16" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="E16" t="n">
-        <v>-58.53018372703412</v>
+        <v>-59.05511811023622</v>
       </c>
       <c r="F16" t="n">
         <v>40</v>
@@ -931,10 +931,10 @@
         <v>24.37</v>
       </c>
       <c r="D19" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.05949938448913</v>
+        <v>-15.46983996717275</v>
       </c>
       <c r="F19" t="n">
         <v>58</v>
@@ -958,10 +958,10 @@
         <v>23.54</v>
       </c>
       <c r="D20" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="E20" t="n">
-        <v>-45.62446898895497</v>
+        <v>-47.32370433305012</v>
       </c>
       <c r="F20" t="n">
         <v>54</v>
@@ -991,7 +991,7 @@
         <v>26.79856115107913</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
         <v>70.48999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E22" t="n">
-        <v>124.1452688324585</v>
+        <v>115.633423180593</v>
       </c>
       <c r="F22" t="n">
         <v>54</v>
@@ -1039,10 +1039,10 @@
         <v>43.75</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>30.25</v>
       </c>
       <c r="E23" t="n">
-        <v>-31.42857142857143</v>
+        <v>-30.85714285714285</v>
       </c>
       <c r="F23" t="n">
         <v>48</v>
@@ -1066,10 +1066,10 @@
         <v>10.2</v>
       </c>
       <c r="D24" t="n">
-        <v>35.75</v>
+        <v>35.5</v>
       </c>
       <c r="E24" t="n">
-        <v>250.4901960784314</v>
+        <v>248.0392156862745</v>
       </c>
       <c r="F24" t="n">
         <v>60</v>
@@ -1093,10 +1093,10 @@
         <v>20.18</v>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.847373637264617</v>
+        <v>-6.838453914767091</v>
       </c>
       <c r="F25" t="n">
         <v>48</v>
@@ -1120,10 +1120,10 @@
         <v>7.64</v>
       </c>
       <c r="D26" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="E26" t="n">
-        <v>-31.282722513089</v>
+        <v>-29.9738219895288</v>
       </c>
       <c r="F26" t="n">
         <v>30</v>
@@ -1147,10 +1147,10 @@
         <v>8.17</v>
       </c>
       <c r="D27" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="E27" t="n">
-        <v>-73.56181150550796</v>
+        <v>-73.80660954712361</v>
       </c>
       <c r="F27" t="n">
         <v>40</v>
@@ -1174,13 +1174,13 @@
         <v>53.84</v>
       </c>
       <c r="D28" t="n">
-        <v>45.5</v>
+        <v>47.25</v>
       </c>
       <c r="E28" t="n">
-        <v>-15.49034175334324</v>
+        <v>-12.23997028231798</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
         <v>25.42</v>
       </c>
       <c r="D29" t="n">
-        <v>19.1</v>
+        <v>19.6</v>
       </c>
       <c r="E29" t="n">
-        <v>-24.86231313926043</v>
+        <v>-22.89535798583792</v>
       </c>
       <c r="F29" t="n">
         <v>30</v>

--- a/portfolio_eak_analysis_report.xlsx
+++ b/portfolio_eak_analysis_report.xlsx
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D2" t="n">
-        <v>10.18</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.1</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>4072</v>
+        <v>4980</v>
       </c>
       <c r="G2" t="n">
-        <v>3640</v>
+        <v>4525</v>
       </c>
       <c r="H2" t="n">
         <v>11</v>
@@ -580,16 +580,16 @@
         <v>8.25</v>
       </c>
       <c r="J2" t="n">
-        <v>30.9090909090909</v>
+        <v>29.09090909090912</v>
       </c>
       <c r="K2" t="n">
-        <v>-432</v>
+        <v>-455</v>
       </c>
       <c r="L2" t="n">
-        <v>-10.6090373280943</v>
+        <v>-9.136546184738958</v>
       </c>
       <c r="M2" t="n">
-        <v>80.40909090909091</v>
+        <v>83.59090909090909</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4.666667</v>
+        <v>4.6410255</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="Q2" t="n">
         <v>11.9160004</v>
@@ -609,7 +609,7 @@
         <v>0.1924</v>
       </c>
       <c r="S2" t="n">
-        <v>38.88890654951316</v>
+        <v>25.00005960455951</v>
       </c>
     </row>
     <row r="3">
@@ -658,14 +658,14 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Accumulate</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>10.845771</v>
       </c>
       <c r="P3" t="n">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="Q3" t="n">
         <v>29.197</v>
@@ -674,7 +674,7 @@
         <v>0.18821</v>
       </c>
       <c r="S3" t="n">
-        <v>45.16126650550578</v>
+        <v>46.66664971243504</v>
       </c>
     </row>
     <row r="4">
@@ -695,13 +695,13 @@
         <v>4.65</v>
       </c>
       <c r="E4" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="F4" t="n">
         <v>465.0000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H4" t="n">
         <v>4.48</v>
@@ -710,16 +710,16 @@
         <v>3.44</v>
       </c>
       <c r="J4" t="n">
-        <v>42.30769230769229</v>
+        <v>44.23076923076921</v>
       </c>
       <c r="K4" t="n">
-        <v>-77.00000000000006</v>
+        <v>-75.00000000000006</v>
       </c>
       <c r="L4" t="n">
-        <v>-16.55913978494624</v>
+        <v>-16.12903225806452</v>
       </c>
       <c r="M4" t="n">
-        <v>63.26923076923077</v>
+        <v>63.07692307692308</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>9.023256</v>
+        <v>9.069768</v>
       </c>
       <c r="P4" t="n">
-        <v>6.38</v>
+        <v>6.41</v>
       </c>
       <c r="Q4" t="n">
         <v>8.8240005</v>
@@ -739,7 +739,7 @@
         <v>1.01229</v>
       </c>
       <c r="S4" t="n">
-        <v>52.94120534477741</v>
+        <v>55.55557763132711</v>
       </c>
     </row>
     <row r="5">
@@ -760,13 +760,13 @@
         <v>4.83</v>
       </c>
       <c r="E5" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="F5" t="n">
         <v>9466.799999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>27048</v>
+        <v>26460</v>
       </c>
       <c r="H5" t="n">
         <v>14.9</v>
@@ -775,16 +775,16 @@
         <v>10.1</v>
       </c>
       <c r="J5" t="n">
-        <v>77.08333333333334</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>17581.2</v>
+        <v>16993.2</v>
       </c>
       <c r="L5" t="n">
-        <v>185.7142857142857</v>
+        <v>179.5031055900621</v>
       </c>
       <c r="M5" t="n">
-        <v>33.29166666666666</v>
+        <v>36.91666666666667</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>51.11111</v>
+        <v>49.999996</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
         <v>12.203</v>
@@ -804,7 +804,7 @@
         <v>5.77067</v>
       </c>
       <c r="S5" t="n">
-        <v>45.45454545454546</v>
+        <v>28.57142208384348</v>
       </c>
     </row>
     <row r="6">
@@ -825,31 +825,31 @@
         <v>2.94</v>
       </c>
       <c r="E6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="F6" t="n">
         <v>4410</v>
       </c>
       <c r="G6" t="n">
-        <v>1905</v>
+        <v>1920</v>
       </c>
       <c r="H6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="I6" t="n">
         <v>1.25</v>
       </c>
       <c r="J6" t="n">
-        <v>16.66666666666666</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>-2505</v>
+        <v>-2490</v>
       </c>
       <c r="L6" t="n">
-        <v>-56.80272108843537</v>
+        <v>-56.4625850340136</v>
       </c>
       <c r="M6" t="n">
-        <v>65.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>15.875</v>
+        <v>16</v>
       </c>
       <c r="P6" t="n">
         <v>78</v>
@@ -869,7 +869,7 @@
         <v>0.4997</v>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -890,13 +890,13 @@
         <v>14.52</v>
       </c>
       <c r="E7" t="n">
-        <v>34.5</v>
+        <v>35.25</v>
       </c>
       <c r="F7" t="n">
         <v>1452</v>
       </c>
       <c r="G7" t="n">
-        <v>3450</v>
+        <v>3525</v>
       </c>
       <c r="H7" t="n">
         <v>40.75</v>
@@ -905,16 +905,16 @@
         <v>24.2</v>
       </c>
       <c r="J7" t="n">
-        <v>62.2356495468278</v>
+        <v>66.76737160120845</v>
       </c>
       <c r="K7" t="n">
-        <v>1998</v>
+        <v>2073</v>
       </c>
       <c r="L7" t="n">
-        <v>137.603305785124</v>
+        <v>142.7685950413223</v>
       </c>
       <c r="M7" t="n">
-        <v>37.77643504531722</v>
+        <v>37.32326283987916</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>16.586538</v>
+        <v>16.947117</v>
       </c>
       <c r="P7" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="Q7" t="n">
         <v>2.866</v>
@@ -934,7 +934,7 @@
         <v>1.59067</v>
       </c>
       <c r="S7" t="n">
-        <v>22.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -955,13 +955,13 @@
         <v>11.8</v>
       </c>
       <c r="E8" t="n">
-        <v>9.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>12980</v>
       </c>
       <c r="G8" t="n">
-        <v>10065</v>
+        <v>10120</v>
       </c>
       <c r="H8" t="n">
         <v>9.5</v>
@@ -970,16 +970,16 @@
         <v>8.5</v>
       </c>
       <c r="J8" t="n">
-        <v>65.00000000000003</v>
+        <v>69.99999999999993</v>
       </c>
       <c r="K8" t="n">
-        <v>-2915</v>
+        <v>-2860</v>
       </c>
       <c r="L8" t="n">
-        <v>-22.45762711864407</v>
+        <v>-22.03389830508476</v>
       </c>
       <c r="M8" t="n">
-        <v>83.5</v>
+        <v>83</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>11.158536</v>
+        <v>11.219512</v>
       </c>
       <c r="P8" t="n">
         <v>6.52</v>
@@ -999,7 +999,7 @@
         <v>0.35826</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -1020,13 +1020,13 @@
         <v>16.19</v>
       </c>
       <c r="E9" t="n">
-        <v>7.05</v>
+        <v>7.15</v>
       </c>
       <c r="F9" t="n">
         <v>8095.000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>3525</v>
+        <v>3575</v>
       </c>
       <c r="H9" t="n">
         <v>8.6</v>
@@ -1035,16 +1035,16 @@
         <v>5.75</v>
       </c>
       <c r="J9" t="n">
-        <v>45.61403508771929</v>
+        <v>49.12280701754388</v>
       </c>
       <c r="K9" t="n">
-        <v>-4570.000000000001</v>
+        <v>-4520.000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-56.45460160592959</v>
+        <v>-55.83693638048178</v>
       </c>
       <c r="M9" t="n">
-        <v>38.43859649122807</v>
+        <v>38.08771929824562</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>12.589286</v>
+        <v>12.767858</v>
       </c>
       <c r="P9" t="n">
-        <v>7.09</v>
+        <v>6.99</v>
       </c>
       <c r="Q9" t="n">
         <v>4.066</v>
@@ -1064,7 +1064,7 @@
         <v>1.96118</v>
       </c>
       <c r="S9" t="n">
-        <v>53.8461651322305</v>
+        <v>52.00000610351097</v>
       </c>
     </row>
     <row r="10">
@@ -1085,13 +1085,13 @@
         <v>27.32</v>
       </c>
       <c r="E10" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="F10" t="n">
         <v>17129.64</v>
       </c>
       <c r="G10" t="n">
-        <v>10721.7</v>
+        <v>10909.8</v>
       </c>
       <c r="H10" t="n">
         <v>22.5</v>
@@ -1100,16 +1100,16 @@
         <v>13.4</v>
       </c>
       <c r="J10" t="n">
-        <v>40.65934065934067</v>
+        <v>43.95604395604394</v>
       </c>
       <c r="K10" t="n">
-        <v>-6407.939999999999</v>
+        <v>-6219.84</v>
       </c>
       <c r="L10" t="n">
-        <v>-37.40849194729135</v>
+        <v>-36.3103953147877</v>
       </c>
       <c r="M10" t="n">
-        <v>58.43406593406593</v>
+        <v>58.10439560439561</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>10.058824</v>
+        <v>10.235293</v>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
         <v>15.274</v>
@@ -1129,7 +1129,7 @@
         <v>2.16375</v>
       </c>
       <c r="S10" t="n">
-        <v>74.1379239471316</v>
+        <v>73.21427507060169</v>
       </c>
     </row>
     <row r="11">
@@ -1150,13 +1150,13 @@
         <v>26.36</v>
       </c>
       <c r="E11" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F11" t="n">
         <v>10544</v>
       </c>
       <c r="G11" t="n">
-        <v>5560</v>
+        <v>5520</v>
       </c>
       <c r="H11" t="n">
         <v>16.6</v>
@@ -1165,16 +1165,16 @@
         <v>10.6</v>
       </c>
       <c r="J11" t="n">
-        <v>54.99999999999999</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="K11" t="n">
-        <v>-4984</v>
+        <v>-5024</v>
       </c>
       <c r="L11" t="n">
-        <v>-47.26858877086494</v>
+        <v>-47.64795144157814</v>
       </c>
       <c r="M11" t="n">
-        <v>78.5</v>
+        <v>78.66666666666667</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>11.300813</v>
+        <v>11.219512</v>
       </c>
       <c r="P11" t="n">
-        <v>7.69</v>
+        <v>7.97</v>
       </c>
       <c r="Q11" t="n">
         <v>22.702</v>
@@ -1194,7 +1194,7 @@
         <v>0.48252</v>
       </c>
       <c r="S11" t="n">
-        <v>69.04761310067009</v>
+        <v>67.44186355978741</v>
       </c>
     </row>
     <row r="12">
@@ -1215,13 +1215,13 @@
         <v>12.39</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F12" t="n">
         <v>12390</v>
       </c>
       <c r="G12" t="n">
-        <v>11000</v>
+        <v>11100</v>
       </c>
       <c r="H12" t="n">
         <v>11.4</v>
@@ -1230,16 +1230,16 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>76.47058823529412</v>
+        <v>82.35294117647057</v>
       </c>
       <c r="K12" t="n">
-        <v>-1390</v>
+        <v>-1290</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.21872477804682</v>
+        <v>-10.41162227602906</v>
       </c>
       <c r="M12" t="n">
-        <v>77.35294117647058</v>
+        <v>72.76470588235294</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>12.087912</v>
+        <v>12.197803</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>7.93</v>
       </c>
       <c r="Q12" t="n">
         <v>12.638</v>
@@ -1259,7 +1259,7 @@
         <v>0.471</v>
       </c>
       <c r="S12" t="n">
-        <v>39.99992370576365</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -1315,13 +1315,13 @@
         <v>5.51</v>
       </c>
       <c r="E14" t="n">
-        <v>8.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>551</v>
       </c>
       <c r="G14" t="n">
-        <v>875</v>
+        <v>880.0000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>8.9</v>
@@ -1330,16 +1330,16 @@
         <v>5.5</v>
       </c>
       <c r="J14" t="n">
-        <v>95.58823529411764</v>
+        <v>97.05882352941177</v>
       </c>
       <c r="K14" t="n">
-        <v>324</v>
+        <v>329.0000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>58.80217785843921</v>
+        <v>59.70961887477316</v>
       </c>
       <c r="M14" t="n">
-        <v>77.44117647058823</v>
+        <v>77.29411764705883</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>9.114584000000001</v>
+        <v>9.166667</v>
       </c>
       <c r="P14" t="n">
-        <v>5.65</v>
+        <v>5.68</v>
       </c>
       <c r="Q14" t="n">
         <v>19.307</v>
@@ -1359,7 +1359,7 @@
         <v>0.76822</v>
       </c>
       <c r="S14" t="n">
-        <v>75.7575564914402</v>
+        <v>76.4705717357505</v>
       </c>
     </row>
     <row r="15">
@@ -1380,13 +1380,13 @@
         <v>23.27</v>
       </c>
       <c r="E15" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="F15" t="n">
         <v>48867</v>
       </c>
       <c r="G15" t="n">
-        <v>21630</v>
+        <v>21210</v>
       </c>
       <c r="H15" t="n">
         <v>11.4</v>
@@ -1395,27 +1395,27 @@
         <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>82.53968253968254</v>
+        <v>79.36507936507937</v>
       </c>
       <c r="K15" t="n">
-        <v>-27237</v>
+        <v>-27657</v>
       </c>
       <c r="L15" t="n">
-        <v>-55.73700042973786</v>
+        <v>-56.59647614954878</v>
       </c>
       <c r="M15" t="n">
-        <v>69.24603174603175</v>
+        <v>72.56349206349206</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Wait/Hold</t>
+          <t>Buy More</t>
         </is>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.287</v>
@@ -1424,7 +1424,7 @@
         <v>0.12099</v>
       </c>
       <c r="S15" t="n">
-        <v>47.78070137826382</v>
+        <v>33.69865028062684</v>
       </c>
     </row>
     <row r="16">
@@ -1519,13 +1519,13 @@
         <v>284</v>
       </c>
       <c r="H17" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="I17" t="n">
         <v>1.15</v>
       </c>
       <c r="J17" t="n">
-        <v>57.44680851063828</v>
+        <v>67.49999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>-129.9999999999999</v>
@@ -1534,7 +1534,7 @@
         <v>-31.40096618357488</v>
       </c>
       <c r="M17" t="n">
-        <v>67.75531914893617</v>
+        <v>66.75</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>0.29902</v>
       </c>
       <c r="S17" t="n">
-        <v>69.23076923076923</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="18">
@@ -1575,13 +1575,13 @@
         <v>42.61</v>
       </c>
       <c r="E18" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="F18" t="n">
         <v>16788.34</v>
       </c>
       <c r="G18" t="n">
-        <v>5831.200000000001</v>
+        <v>5791.799999999999</v>
       </c>
       <c r="H18" t="n">
         <v>26</v>
@@ -1590,16 +1590,16 @@
         <v>13.9</v>
       </c>
       <c r="J18" t="n">
-        <v>7.438016528925623</v>
+        <v>6.611570247933876</v>
       </c>
       <c r="K18" t="n">
-        <v>-10957.14</v>
+        <v>-10996.54</v>
       </c>
       <c r="L18" t="n">
-        <v>-65.2663693968552</v>
+        <v>-65.50105609011969</v>
       </c>
       <c r="M18" t="n">
-        <v>54.25619834710744</v>
+        <v>54.33884297520661</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>16.444445</v>
+        <v>16.333334</v>
       </c>
       <c r="P18" t="n">
-        <v>8.210000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="Q18" t="n">
         <v>3.1140001</v>
@@ -1619,7 +1619,7 @@
         <v>0.57284</v>
       </c>
       <c r="S18" t="n">
-        <v>41.03746670583865</v>
+        <v>37.92170292856077</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +1640,13 @@
         <v>24.37</v>
       </c>
       <c r="E19" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="F19" t="n">
         <v>34118</v>
       </c>
       <c r="G19" t="n">
-        <v>27020</v>
+        <v>26880</v>
       </c>
       <c r="H19" t="n">
         <v>26.5</v>
@@ -1655,16 +1655,16 @@
         <v>18.1</v>
       </c>
       <c r="J19" t="n">
-        <v>14.28571428571428</v>
+        <v>13.09523809523807</v>
       </c>
       <c r="K19" t="n">
-        <v>-7098</v>
+        <v>-7238</v>
       </c>
       <c r="L19" t="n">
-        <v>-20.80426754205991</v>
+        <v>-21.21460812474354</v>
       </c>
       <c r="M19" t="n">
-        <v>65.07142857142857</v>
+        <v>65.19047619047619</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>6.1858974</v>
+        <v>6.1538467</v>
       </c>
       <c r="P19" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
         <v>10.5100006</v>
@@ -1684,7 +1684,7 @@
         <v>2.05188</v>
       </c>
       <c r="S19" t="n">
-        <v>16.66665342118795</v>
+        <v>15.99999694823985</v>
       </c>
     </row>
     <row r="20">
@@ -1705,13 +1705,13 @@
         <v>23.54</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="F20" t="n">
         <v>44726</v>
       </c>
       <c r="G20" t="n">
-        <v>22800</v>
+        <v>22610</v>
       </c>
       <c r="H20" t="n">
         <v>15.6</v>
@@ -1720,27 +1720,27 @@
         <v>10.1</v>
       </c>
       <c r="J20" t="n">
-        <v>34.54545454545455</v>
+        <v>32.72727272727274</v>
       </c>
       <c r="K20" t="n">
-        <v>-21926</v>
+        <v>-22116</v>
       </c>
       <c r="L20" t="n">
-        <v>-49.02293967714528</v>
+        <v>-49.44774851316907</v>
       </c>
       <c r="M20" t="n">
-        <v>69.54545454545455</v>
+        <v>72.72727272727272</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Wait/Hold</t>
+          <t>Buy More</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>12.765958</v>
+        <v>12.6595745</v>
       </c>
       <c r="P20" t="n">
-        <v>4.96</v>
+        <v>5.04</v>
       </c>
       <c r="Q20" t="n">
         <v>10.147</v>
@@ -1749,7 +1749,7 @@
         <v>0.20703</v>
       </c>
       <c r="S20" t="n">
-        <v>45.94594106959532</v>
+        <v>29.99997456866872</v>
       </c>
     </row>
     <row r="21">
@@ -1770,13 +1770,13 @@
         <v>27.8</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>34.75</v>
       </c>
       <c r="F21" t="n">
         <v>5560</v>
       </c>
       <c r="G21" t="n">
-        <v>7000</v>
+        <v>6950</v>
       </c>
       <c r="H21" t="n">
         <v>38</v>
@@ -1785,16 +1785,16 @@
         <v>29.5</v>
       </c>
       <c r="J21" t="n">
-        <v>64.70588235294117</v>
+        <v>61.76470588235294</v>
       </c>
       <c r="K21" t="n">
-        <v>1440</v>
+        <v>1390</v>
       </c>
       <c r="L21" t="n">
-        <v>25.89928057553956</v>
+        <v>25</v>
       </c>
       <c r="M21" t="n">
-        <v>65.02941176470588</v>
+        <v>65.32352941176471</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>11.111111</v>
+        <v>11.031746</v>
       </c>
       <c r="P21" t="n">
         <v>6.04</v>
@@ -1835,13 +1835,13 @@
         <v>70.48999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>147.5</v>
+        <v>149.5</v>
       </c>
       <c r="F22" t="n">
         <v>14098</v>
       </c>
       <c r="G22" t="n">
-        <v>29500</v>
+        <v>29900</v>
       </c>
       <c r="H22" t="n">
         <v>164</v>
@@ -1850,27 +1850,27 @@
         <v>94.25</v>
       </c>
       <c r="J22" t="n">
-        <v>76.34408602150538</v>
+        <v>79.21146953405018</v>
       </c>
       <c r="K22" t="n">
-        <v>15402</v>
+        <v>15802</v>
       </c>
       <c r="L22" t="n">
-        <v>109.2495389416939</v>
+        <v>112.086820825649</v>
       </c>
       <c r="M22" t="n">
-        <v>72.86559139784947</v>
+        <v>69.57885304659499</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Wait/Hold</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>9.716732</v>
+        <v>9.854977</v>
       </c>
       <c r="P22" t="n">
-        <v>6.08</v>
+        <v>5.85</v>
       </c>
       <c r="Q22" t="n">
         <v>11.359999</v>
@@ -1879,7 +1879,7 @@
         <v>0.244</v>
       </c>
       <c r="S22" t="n">
-        <v>33.33333333333333</v>
+        <v>35.71428571428572</v>
       </c>
     </row>
     <row r="23">
@@ -1900,13 +1900,13 @@
         <v>43.75</v>
       </c>
       <c r="E23" t="n">
-        <v>29</v>
+        <v>29.25</v>
       </c>
       <c r="F23" t="n">
         <v>43750</v>
       </c>
       <c r="G23" t="n">
-        <v>29000</v>
+        <v>29250</v>
       </c>
       <c r="H23" t="n">
         <v>32.5</v>
@@ -1915,16 +1915,16 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>58.82352941176471</v>
+        <v>61.76470588235294</v>
       </c>
       <c r="K23" t="n">
-        <v>-14750</v>
+        <v>-14500</v>
       </c>
       <c r="L23" t="n">
-        <v>-33.71428571428572</v>
+        <v>-33.14285714285714</v>
       </c>
       <c r="M23" t="n">
-        <v>71.61764705882354</v>
+        <v>71.32352941176471</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>10.13986</v>
+        <v>10.227273</v>
       </c>
       <c r="P23" t="n">
-        <v>5.42</v>
+        <v>5.47</v>
       </c>
       <c r="Q23" t="n">
         <v>6.418</v>
@@ -1965,31 +1965,31 @@
         <v>10.2</v>
       </c>
       <c r="E24" t="n">
-        <v>32.75</v>
+        <v>32.25</v>
       </c>
       <c r="F24" t="n">
         <v>10200</v>
       </c>
       <c r="G24" t="n">
-        <v>32750</v>
+        <v>32250</v>
       </c>
       <c r="H24" t="n">
         <v>36</v>
       </c>
       <c r="I24" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="J24" t="n">
-        <v>79.03225806451613</v>
+        <v>75.32894736842105</v>
       </c>
       <c r="K24" t="n">
-        <v>22550</v>
+        <v>22050</v>
       </c>
       <c r="L24" t="n">
-        <v>221.078431372549</v>
+        <v>216.1764705882353</v>
       </c>
       <c r="M24" t="n">
-        <v>75.59677419354838</v>
+        <v>75.96710526315789</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>9.492753</v>
+        <v>9.347826</v>
       </c>
       <c r="P24" t="n">
-        <v>11.04</v>
+        <v>11.21</v>
       </c>
       <c r="Q24" t="n">
         <v>10.986</v>
@@ -2009,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>49.73748955528735</v>
+        <v>45.15809304913206</v>
       </c>
     </row>
     <row r="25">
@@ -2054,18 +2054,18 @@
         <v>-8.325074331020812</v>
       </c>
       <c r="M25" t="n">
-        <v>67.53333333333333</v>
+        <v>71.53333333333333</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Wait/Hold</t>
+          <t>Buy More</t>
         </is>
       </c>
       <c r="O25" t="n">
         <v>18.5</v>
       </c>
       <c r="P25" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="Q25" t="n">
         <v>15.302</v>
@@ -2074,7 +2074,7 @@
         <v>0.15896</v>
       </c>
       <c r="S25" t="n">
-        <v>52.6315842308731</v>
+        <v>40.00005086250086</v>
       </c>
     </row>
     <row r="26">
@@ -2130,7 +2130,7 @@
         <v>21.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="Q26" t="n">
         <v>10.2790006</v>
@@ -2139,7 +2139,7 @@
         <v>3.03834</v>
       </c>
       <c r="S26" t="n">
-        <v>57.89473155859794</v>
+        <v>52.94118307040013</v>
       </c>
     </row>
     <row r="27">
@@ -2184,7 +2184,7 @@
         <v>-74.05140758873929</v>
       </c>
       <c r="M27" t="n">
-        <v>53.05128205128205</v>
+        <v>57.05128205128205</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>1.93565</v>
       </c>
       <c r="S27" t="n">
-        <v>55.99997711188189</v>
+        <v>44.99999105933206</v>
       </c>
     </row>
     <row r="28">
@@ -2225,13 +2225,13 @@
         <v>53.84</v>
       </c>
       <c r="E28" t="n">
-        <v>45.25</v>
+        <v>44.75</v>
       </c>
       <c r="F28" t="n">
         <v>5384</v>
       </c>
       <c r="G28" t="n">
-        <v>4525</v>
+        <v>4475</v>
       </c>
       <c r="H28" t="n">
         <v>54.5</v>
@@ -2240,16 +2240,16 @@
         <v>40.5</v>
       </c>
       <c r="J28" t="n">
-        <v>33.92857142857143</v>
+        <v>30.35714285714285</v>
       </c>
       <c r="K28" t="n">
-        <v>-859</v>
+        <v>-909</v>
       </c>
       <c r="L28" t="n">
-        <v>-15.95468053491828</v>
+        <v>-16.88335809806836</v>
       </c>
       <c r="M28" t="n">
-        <v>53.60714285714286</v>
+        <v>57.96428571428572</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>14.596775</v>
+        <v>14.435484</v>
       </c>
       <c r="P28" t="n">
-        <v>3.61</v>
+        <v>3.69</v>
       </c>
       <c r="Q28" t="n">
         <v>9.789999999999999</v>
@@ -2269,7 +2269,7 @@
         <v>1.33418</v>
       </c>
       <c r="S28" t="n">
-        <v>54.83870967741936</v>
+        <v>44.82758620689656</v>
       </c>
     </row>
     <row r="29">
@@ -2290,13 +2290,13 @@
         <v>25.42</v>
       </c>
       <c r="E29" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="F29" t="n">
         <v>5084</v>
       </c>
       <c r="G29" t="n">
-        <v>3740</v>
+        <v>3720</v>
       </c>
       <c r="H29" t="n">
         <v>25.25</v>
@@ -2305,16 +2305,16 @@
         <v>15.8</v>
       </c>
       <c r="J29" t="n">
-        <v>30.68783068783068</v>
+        <v>29.62962962962964</v>
       </c>
       <c r="K29" t="n">
-        <v>-1344</v>
+        <v>-1364</v>
       </c>
       <c r="L29" t="n">
-        <v>-26.43587726199844</v>
+        <v>-26.82926829268293</v>
       </c>
       <c r="M29" t="n">
-        <v>45.93121693121693</v>
+        <v>46.03703703703704</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>16.696428</v>
+        <v>16.607143</v>
       </c>
       <c r="P29" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="Q29" t="n">
         <v>10.017</v>
@@ -2334,7 +2334,7 @@
         <v>1.54054</v>
       </c>
       <c r="S29" t="n">
-        <v>67.61361815863229</v>
+        <v>64.62050676638384</v>
       </c>
     </row>
     <row r="30">
@@ -2355,13 +2355,13 @@
         <v>7.24</v>
       </c>
       <c r="E30" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="F30" t="n">
         <v>2896</v>
       </c>
       <c r="G30" t="n">
-        <v>1528</v>
+        <v>1512</v>
       </c>
       <c r="H30" t="n">
         <v>4.5</v>
@@ -2370,16 +2370,16 @@
         <v>3.18</v>
       </c>
       <c r="J30" t="n">
-        <v>48.48484848484846</v>
+        <v>45.45454545454543</v>
       </c>
       <c r="K30" t="n">
-        <v>-1368</v>
+        <v>-1384</v>
       </c>
       <c r="L30" t="n">
-        <v>-47.23756906077348</v>
+        <v>-47.79005524861879</v>
       </c>
       <c r="M30" t="n">
-        <v>44.15151515151516</v>
+        <v>44.45454545454545</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>12.32258</v>
+        <v>12.193548</v>
       </c>
       <c r="P30" t="n">
-        <v>6.32</v>
+        <v>6.35</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>1.51037</v>
       </c>
       <c r="S30" t="n">
-        <v>61.29032258064516</v>
+        <v>51.72413793103448</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio_eak_analysis_report.xlsx
+++ b/portfolio_eak_analysis_report.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -448,6 +448,16 @@
     <col width="15" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,72 +488,122 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Trend_Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Entry_Zone</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Exit_Zone</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Stop_Loss</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Upside_Pct</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Cost_Value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Market_Value</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>High_52W</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Low_52W</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Gain_Loss_Value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Gain_Loss_Pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Price_Position</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Gain_Loss_Value</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Gain_Loss_Pct</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Total_Score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Advice</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Target_Action</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_Ratio</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Yield</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Entry_Zone_Low</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Entry_Zone_High</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Exit_Zone_Low</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Exit_Zone_High</t>
         </is>
       </c>
     </row>
@@ -567,49 +627,87 @@
       <c r="E2" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8.25 - 8.66</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10.67 - 11.00</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>7.837499999999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.90055248618783</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.336082474226802</v>
+      </c>
+      <c r="L2" t="n">
         <v>4980</v>
       </c>
-      <c r="G2" t="n">
+      <c r="M2" t="n">
         <v>4525</v>
       </c>
-      <c r="H2" t="n">
+      <c r="N2" t="n">
+        <v>-455</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-9.136546184738958</v>
+      </c>
+      <c r="P2" t="n">
+        <v>29.09090909090912</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>83.59090909090909</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 8.66</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>1.654411764705882</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4.6410255</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W2" t="n">
+        <v>11.9160004</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.1924</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>25.00005960455951</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>8.6625</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="AC2" t="n">
         <v>11</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="J2" t="n">
-        <v>29.09090909090912</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-455</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-9.136546184738958</v>
-      </c>
-      <c r="M2" t="n">
-        <v>83.59090909090909</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>4.6410255</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>11.9160004</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.1924</v>
-      </c>
-      <c r="S2" t="n">
-        <v>25.00005960455951</v>
       </c>
     </row>
     <row r="3">
@@ -632,49 +730,87 @@
       <c r="E3" t="n">
         <v>21.8</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>21.10 - 22.16</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34.92 - 36.00</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>20.045</v>
+      </c>
+      <c r="J3" t="n">
+        <v>60.18348623853211</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.475783475783481</v>
+      </c>
+      <c r="L3" t="n">
         <v>1302</v>
       </c>
-      <c r="G3" t="n">
+      <c r="M3" t="n">
         <v>2180</v>
       </c>
-      <c r="H3" t="n">
+      <c r="N3" t="n">
+        <v>878</v>
+      </c>
+      <c r="O3" t="n">
+        <v>67.4347158218126</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.697986577181204</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>87.53020134228188</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Accumulate</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Buy Now (Good RRR)</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>0.5100937903141453</v>
+      </c>
+      <c r="U3" t="n">
+        <v>10.845771</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W3" t="n">
+        <v>29.197</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.18821</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>46.66664971243504</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>22.155</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="AC3" t="n">
         <v>36</v>
-      </c>
-      <c r="I3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.697986577181204</v>
-      </c>
-      <c r="K3" t="n">
-        <v>878</v>
-      </c>
-      <c r="L3" t="n">
-        <v>67.4347158218126</v>
-      </c>
-      <c r="M3" t="n">
-        <v>87.53020134228188</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Accumulate</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>10.845771</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>29.197</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.18821</v>
-      </c>
-      <c r="S3" t="n">
-        <v>46.66664971243504</v>
       </c>
     </row>
     <row r="4">
@@ -697,49 +833,87 @@
       <c r="E4" t="n">
         <v>3.9</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3.44 - 3.61</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4.35 - 4.48</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.268</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11.42564102564103</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.7050632911392407</v>
+      </c>
+      <c r="L4" t="n">
         <v>465.0000000000001</v>
       </c>
-      <c r="G4" t="n">
+      <c r="M4" t="n">
         <v>390</v>
       </c>
-      <c r="H4" t="n">
+      <c r="N4" t="n">
+        <v>-75.00000000000006</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-16.12903225806452</v>
+      </c>
+      <c r="P4" t="n">
+        <v>44.23076923076921</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>63.07692307692308</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>0.4947744410636328</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9.069768</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="W4" t="n">
+        <v>8.8240005</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01229</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>55.55557763132711</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.612</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4.3456</v>
+      </c>
+      <c r="AC4" t="n">
         <v>4.48</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="J4" t="n">
-        <v>44.23076923076921</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-75.00000000000006</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-16.12903225806452</v>
-      </c>
-      <c r="M4" t="n">
-        <v>63.07692307692308</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>9.069768</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>8.8240005</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.01229</v>
-      </c>
-      <c r="S4" t="n">
-        <v>55.55557763132711</v>
       </c>
     </row>
     <row r="5">
@@ -762,49 +936,87 @@
       <c r="E5" t="n">
         <v>13.5</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10.10 - 10.61</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>14.45 - 14.90</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>9.594999999999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7.059259259259256</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2440460947503199</v>
+      </c>
+      <c r="L5" t="n">
         <v>9466.799999999999</v>
       </c>
-      <c r="G5" t="n">
+      <c r="M5" t="n">
         <v>26460</v>
       </c>
-      <c r="H5" t="n">
+      <c r="N5" t="n">
+        <v>16993.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>179.5031055900621</v>
+      </c>
+      <c r="P5" t="n">
+        <v>70.83333333333333</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>36.91666666666667</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Reduce 50%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>1.726049874415068</v>
+      </c>
+      <c r="U5" t="n">
+        <v>49.999996</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>12.203</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5.77067</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>28.57142208384348</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>10.605</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>14.453</v>
+      </c>
+      <c r="AC5" t="n">
         <v>14.9</v>
-      </c>
-      <c r="I5" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>70.83333333333333</v>
-      </c>
-      <c r="K5" t="n">
-        <v>16993.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>179.5031055900621</v>
-      </c>
-      <c r="M5" t="n">
-        <v>36.91666666666667</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>49.999996</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>12.203</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5.77067</v>
-      </c>
-      <c r="S5" t="n">
-        <v>28.57142208384348</v>
       </c>
     </row>
     <row r="6">
@@ -827,49 +1039,87 @@
       <c r="E6" t="n">
         <v>1.28</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.25 - 1.31</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.31 - 1.35</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.304687500000006</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3189189189189197</v>
+      </c>
+      <c r="L6" t="n">
         <v>4410</v>
       </c>
-      <c r="G6" t="n">
+      <c r="M6" t="n">
         <v>1920</v>
       </c>
-      <c r="H6" t="n">
+      <c r="N6" t="n">
+        <v>-2490</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-56.4625850340136</v>
+      </c>
+      <c r="P6" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>60</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>0.6505659032171821</v>
+      </c>
+      <c r="U6" t="n">
+        <v>16</v>
+      </c>
+      <c r="V6" t="n">
+        <v>78</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4997</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.3095</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1.35</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J6" t="n">
-        <v>30</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-2490</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-56.4625850340136</v>
-      </c>
-      <c r="M6" t="n">
-        <v>60</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>16</v>
-      </c>
-      <c r="P6" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.4997</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -892,49 +1142,87 @@
       <c r="E7" t="n">
         <v>35.25</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>24.20 - 25.41</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>39.53 - 40.75</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12.13475177304963</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3488988580750405</v>
+      </c>
+      <c r="L7" t="n">
         <v>1452</v>
       </c>
-      <c r="G7" t="n">
+      <c r="M7" t="n">
         <v>3525</v>
       </c>
-      <c r="H7" t="n">
+      <c r="N7" t="n">
+        <v>2073</v>
+      </c>
+      <c r="O7" t="n">
+        <v>142.7685950413223</v>
+      </c>
+      <c r="P7" t="n">
+        <v>66.76737160120845</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>37.32326283987916</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Reduce 50%</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>1.114109634070372</v>
+      </c>
+      <c r="U7" t="n">
+        <v>16.947117</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.866</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.59067</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>39.5275</v>
+      </c>
+      <c r="AC7" t="n">
         <v>40.75</v>
-      </c>
-      <c r="I7" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>66.76737160120845</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2073</v>
-      </c>
-      <c r="L7" t="n">
-        <v>142.7685950413223</v>
-      </c>
-      <c r="M7" t="n">
-        <v>37.32326283987916</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>16.947117</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.866</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.59067</v>
-      </c>
-      <c r="S7" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -957,49 +1245,87 @@
       <c r="E8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bullish 📈</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8.50 - 8.93</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9.21 - 9.50</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.074999999999999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1630434782608758</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.01333333333333384</v>
+      </c>
+      <c r="L8" t="n">
         <v>12980</v>
       </c>
-      <c r="G8" t="n">
+      <c r="M8" t="n">
         <v>10120</v>
       </c>
-      <c r="H8" t="n">
+      <c r="N8" t="n">
+        <v>-2860</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-22.03389830508476</v>
+      </c>
+      <c r="P8" t="n">
+        <v>69.99999999999993</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>83</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 8.93</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0.5044673074319751</v>
+      </c>
+      <c r="U8" t="n">
+        <v>11.219512</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="W8" t="n">
+        <v>20.212</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8.925000000000001</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9.215</v>
+      </c>
+      <c r="AC8" t="n">
         <v>9.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>69.99999999999993</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-2860</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-22.03389830508476</v>
-      </c>
-      <c r="M8" t="n">
-        <v>83</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>11.219512</v>
-      </c>
-      <c r="P8" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>20.212</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.35826</v>
-      </c>
-      <c r="S8" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -1022,49 +1348,87 @@
       <c r="E9" t="n">
         <v>7.15</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5.75 - 6.04</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8.34 - 8.60</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5.462499999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16.67132867132865</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7063703703703691</v>
+      </c>
+      <c r="L9" t="n">
         <v>8095.000000000001</v>
       </c>
-      <c r="G9" t="n">
+      <c r="M9" t="n">
         <v>3575</v>
       </c>
-      <c r="H9" t="n">
+      <c r="N9" t="n">
+        <v>-4520.000000000001</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-55.83693638048178</v>
+      </c>
+      <c r="P9" t="n">
+        <v>49.12280701754388</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>38.08771929824562</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Reduce/Cut</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Reduce 50%</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>0.7494745416571122</v>
+      </c>
+      <c r="U9" t="n">
+        <v>12.767858</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.066</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.96118</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>52.00000610351097</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>6.037500000000001</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.341999999999999</v>
+      </c>
+      <c r="AC9" t="n">
         <v>8.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J9" t="n">
-        <v>49.12280701754388</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-4520.000000000001</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-55.83693638048178</v>
-      </c>
-      <c r="M9" t="n">
-        <v>38.08771929824562</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Reduce/Cut</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>12.767858</v>
-      </c>
-      <c r="P9" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.066</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.96118</v>
-      </c>
-      <c r="S9" t="n">
-        <v>52.00000610351097</v>
       </c>
     </row>
     <row r="10">
@@ -1087,49 +1451,87 @@
       <c r="E10" t="n">
         <v>17.4</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>13.40 - 14.07</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>21.82 - 22.50</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25.43103448275862</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9475374732334052</v>
+      </c>
+      <c r="L10" t="n">
         <v>17129.64</v>
       </c>
-      <c r="G10" t="n">
+      <c r="M10" t="n">
         <v>10909.8</v>
       </c>
-      <c r="H10" t="n">
+      <c r="N10" t="n">
+        <v>-6219.84</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-36.3103953147877</v>
+      </c>
+      <c r="P10" t="n">
+        <v>43.95604395604394</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>58.10439560439561</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>1.753504815587212</v>
+      </c>
+      <c r="U10" t="n">
+        <v>10.235293</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W10" t="n">
+        <v>15.274</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.16375</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>73.21427507060169</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>21.825</v>
+      </c>
+      <c r="AC10" t="n">
         <v>22.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>43.95604395604394</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-6219.84</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-36.3103953147877</v>
-      </c>
-      <c r="M10" t="n">
-        <v>58.10439560439561</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>10.235293</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>15.274</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.16375</v>
-      </c>
-      <c r="S10" t="n">
-        <v>73.21427507060169</v>
       </c>
     </row>
     <row r="11">
@@ -1152,49 +1554,87 @@
       <c r="E11" t="n">
         <v>13.8</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bullish 📈</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>10.60 - 11.13</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>16.10 - 16.60</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16.68115942028985</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6171581769436992</v>
+      </c>
+      <c r="L11" t="n">
         <v>10544</v>
       </c>
-      <c r="G11" t="n">
+      <c r="M11" t="n">
         <v>5520</v>
       </c>
-      <c r="H11" t="n">
+      <c r="N11" t="n">
+        <v>-5024</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-47.64795144157814</v>
+      </c>
+      <c r="P11" t="n">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>78.66666666666667</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 11.13</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4471034237649568</v>
+      </c>
+      <c r="U11" t="n">
+        <v>11.219512</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="W11" t="n">
+        <v>22.702</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.48252</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>67.44186355978741</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>16.102</v>
+      </c>
+      <c r="AC11" t="n">
         <v>16.6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>53.33333333333334</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-5024</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-47.64795144157814</v>
-      </c>
-      <c r="M11" t="n">
-        <v>78.66666666666667</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>11.219512</v>
-      </c>
-      <c r="P11" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>22.702</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.48252</v>
-      </c>
-      <c r="S11" t="n">
-        <v>67.44186355978741</v>
       </c>
     </row>
     <row r="12">
@@ -1217,49 +1657,87 @@
       <c r="E12" t="n">
         <v>11.1</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>9.70 - 10.19</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>11.06 - 11.40</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9.214999999999998</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.3783783783783767</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.0222811671087532</v>
+      </c>
+      <c r="L12" t="n">
         <v>12390</v>
       </c>
-      <c r="G12" t="n">
+      <c r="M12" t="n">
         <v>11100</v>
       </c>
-      <c r="H12" t="n">
+      <c r="N12" t="n">
+        <v>-1290</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-10.41162227602906</v>
+      </c>
+      <c r="P12" t="n">
+        <v>82.35294117647057</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>72.76470588235294</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 10.19</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>0.8565034001893777</v>
+      </c>
+      <c r="U12" t="n">
+        <v>12.197803</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="W12" t="n">
+        <v>12.638</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>10.185</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11.058</v>
+      </c>
+      <c r="AC12" t="n">
         <v>11.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J12" t="n">
-        <v>82.35294117647057</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-1290</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-10.41162227602906</v>
-      </c>
-      <c r="M12" t="n">
-        <v>72.76470588235294</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>12.197803</v>
-      </c>
-      <c r="P12" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>12.638</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="S12" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -1276,26 +1754,48 @@
         <v>22.85</v>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>27420</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>27420</v>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>No Data</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>No Data</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1317,49 +1817,87 @@
       <c r="E14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bullish 📈</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>5.50 - 5.78</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>8.63 - 8.90</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.225</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-1.89772727272727</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.04671328671328664</v>
+      </c>
+      <c r="L14" t="n">
         <v>551</v>
       </c>
-      <c r="G14" t="n">
+      <c r="M14" t="n">
         <v>880.0000000000001</v>
       </c>
-      <c r="H14" t="n">
+      <c r="N14" t="n">
+        <v>329.0000000000001</v>
+      </c>
+      <c r="O14" t="n">
+        <v>59.70961887477316</v>
+      </c>
+      <c r="P14" t="n">
+        <v>97.05882352941177</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>77.29411764705883</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>TP 50% @ 8.63</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4054405121573585</v>
+      </c>
+      <c r="U14" t="n">
+        <v>9.166667</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="W14" t="n">
+        <v>19.307</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.76822</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>76.4705717357505</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.775</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8.633000000000001</v>
+      </c>
+      <c r="AC14" t="n">
         <v>8.9</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>97.05882352941177</v>
-      </c>
-      <c r="K14" t="n">
-        <v>329.0000000000001</v>
-      </c>
-      <c r="L14" t="n">
-        <v>59.70961887477316</v>
-      </c>
-      <c r="M14" t="n">
-        <v>77.29411764705883</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>9.166667</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>19.307</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.76822</v>
-      </c>
-      <c r="S14" t="n">
-        <v>76.4705717357505</v>
       </c>
     </row>
     <row r="15">
@@ -1382,49 +1920,87 @@
       <c r="E15" t="n">
         <v>10.1</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5.10 - 5.35</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>11.06 - 11.40</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.845</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9.485148514851486</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.182302568981922</v>
+      </c>
+      <c r="L15" t="n">
         <v>48867</v>
       </c>
-      <c r="G15" t="n">
+      <c r="M15" t="n">
         <v>21210</v>
       </c>
-      <c r="H15" t="n">
+      <c r="N15" t="n">
+        <v>-27657</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-56.59647614954878</v>
+      </c>
+      <c r="P15" t="n">
+        <v>79.36507936507937</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>72.56349206349206</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 5.35</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0.6275624959835486</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.287</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.12099</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>33.69865028062684</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.355</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11.058</v>
+      </c>
+      <c r="AC15" t="n">
         <v>11.4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>79.36507936507937</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-27657</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-56.59647614954878</v>
-      </c>
-      <c r="M15" t="n">
-        <v>72.56349206349206</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-0.287</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.12099</v>
-      </c>
-      <c r="S15" t="n">
-        <v>33.69865028062684</v>
       </c>
     </row>
     <row r="16">
@@ -1447,49 +2023,87 @@
       <c r="E16" t="n">
         <v>1.57</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1.46 - 1.53</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2.02 - 2.08</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="J16" t="n">
+        <v>28.50955414012737</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.44590163934426</v>
+      </c>
+      <c r="L16" t="n">
         <v>381</v>
       </c>
-      <c r="G16" t="n">
+      <c r="M16" t="n">
         <v>157</v>
       </c>
-      <c r="H16" t="n">
+      <c r="N16" t="n">
+        <v>-224</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-58.79265091863518</v>
+      </c>
+      <c r="P16" t="n">
+        <v>17.74193548387098</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>50.2258064516129</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0.4050161482731531</v>
+      </c>
+      <c r="U16" t="n">
+        <v>78.50001</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.31299999</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.8566400000000001</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>33.33346578717317</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.0176</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.08</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17.74193548387098</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-224</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-58.79265091863518</v>
-      </c>
-      <c r="M16" t="n">
-        <v>50.2258064516129</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>78.50001</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.31299999</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.8566400000000001</v>
-      </c>
-      <c r="S16" t="n">
-        <v>33.33346578717317</v>
       </c>
     </row>
     <row r="17">
@@ -1512,49 +2126,87 @@
       <c r="E17" t="n">
         <v>1.42</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bullish 📈</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.15 - 1.21</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.50 - 1.55</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.0925</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.880281690140855</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.254961832061069</v>
+      </c>
+      <c r="L17" t="n">
         <v>413.9999999999999</v>
       </c>
-      <c r="G17" t="n">
+      <c r="M17" t="n">
         <v>284</v>
       </c>
-      <c r="H17" t="n">
+      <c r="N17" t="n">
+        <v>-129.9999999999999</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-31.40096618357488</v>
+      </c>
+      <c r="P17" t="n">
+        <v>67.49999999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>2.2144821053118</v>
+      </c>
+      <c r="U17" t="n">
+        <v>8.875</v>
+      </c>
+      <c r="V17" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="W17" t="n">
+        <v>5.804</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.2075</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.5035</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.55</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J17" t="n">
-        <v>67.49999999999999</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-129.9999999999999</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-31.40096618357488</v>
-      </c>
-      <c r="M17" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>8.875</v>
-      </c>
-      <c r="P17" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.804</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.29902</v>
-      </c>
-      <c r="S17" t="n">
-        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="18">
@@ -1577,49 +2229,87 @@
       <c r="E18" t="n">
         <v>14.7</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>13.90 - 14.60</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>25.22 - 26.00</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>13.205</v>
+      </c>
+      <c r="J18" t="n">
+        <v>71.56462585034014</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.036789297658866</v>
+      </c>
+      <c r="L18" t="n">
         <v>16788.34</v>
       </c>
-      <c r="G18" t="n">
+      <c r="M18" t="n">
         <v>5791.799999999999</v>
       </c>
-      <c r="H18" t="n">
+      <c r="N18" t="n">
+        <v>-10996.54</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-65.50105609011969</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6.611570247933876</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>54.33884297520661</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>0.4781806021347391</v>
+      </c>
+      <c r="U18" t="n">
+        <v>16.333334</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.1140001</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.57284</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>37.92170292856077</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>14.595</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AC18" t="n">
         <v>26</v>
-      </c>
-      <c r="I18" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>6.611570247933876</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-10996.54</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-65.50105609011969</v>
-      </c>
-      <c r="M18" t="n">
-        <v>54.33884297520661</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>16.333334</v>
-      </c>
-      <c r="P18" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.1140001</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.57284</v>
-      </c>
-      <c r="S18" t="n">
-        <v>37.92170292856077</v>
       </c>
     </row>
     <row r="19">
@@ -1642,49 +2332,87 @@
       <c r="E19" t="n">
         <v>19.2</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>18.10 - 19.01</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>25.70 - 26.50</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>17.195</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33.88020833333333</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.244389027431422</v>
+      </c>
+      <c r="L19" t="n">
         <v>34118</v>
       </c>
-      <c r="G19" t="n">
+      <c r="M19" t="n">
         <v>26880</v>
       </c>
-      <c r="H19" t="n">
+      <c r="N19" t="n">
+        <v>-7238</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-21.21460812474354</v>
+      </c>
+      <c r="P19" t="n">
+        <v>13.09523809523807</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>65.19047619047619</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>1.09724800305792</v>
+      </c>
+      <c r="U19" t="n">
+        <v>6.1538467</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>10.5100006</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.05188</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.99999694823985</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>19.005</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>25.705</v>
+      </c>
+      <c r="AC19" t="n">
         <v>26.5</v>
-      </c>
-      <c r="I19" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>13.09523809523807</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-7238</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-21.21460812474354</v>
-      </c>
-      <c r="M19" t="n">
-        <v>65.19047619047619</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>6.1538467</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>10.5100006</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.05188</v>
-      </c>
-      <c r="S19" t="n">
-        <v>15.99999694823985</v>
       </c>
     </row>
     <row r="20">
@@ -1707,49 +2435,87 @@
       <c r="E20" t="n">
         <v>11.9</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>10.10 - 10.61</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>15.13 - 15.60</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>9.594999999999999</v>
+      </c>
+      <c r="J20" t="n">
+        <v>27.15966386554621</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.402169197396962</v>
+      </c>
+      <c r="L20" t="n">
         <v>44726</v>
       </c>
-      <c r="G20" t="n">
+      <c r="M20" t="n">
         <v>22610</v>
       </c>
-      <c r="H20" t="n">
+      <c r="N20" t="n">
+        <v>-22116</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-49.44774851316907</v>
+      </c>
+      <c r="P20" t="n">
+        <v>32.72727272727274</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>72.72727272727272</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 10.61</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>0.5288999986035275</v>
+      </c>
+      <c r="U20" t="n">
+        <v>12.6595745</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>10.147</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.20703</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>29.99997456866872</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>10.605</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>15.132</v>
+      </c>
+      <c r="AC20" t="n">
         <v>15.6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>32.72727272727274</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-22116</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-49.44774851316907</v>
-      </c>
-      <c r="M20" t="n">
-        <v>72.72727272727272</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>12.6595745</v>
-      </c>
-      <c r="P20" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>10.147</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.20703</v>
-      </c>
-      <c r="S20" t="n">
-        <v>29.99997456866872</v>
       </c>
     </row>
     <row r="21">
@@ -1772,49 +2538,87 @@
       <c r="E21" t="n">
         <v>34.75</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>29.50 - 30.98</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>36.86 - 38.00</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>28.025</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6.071942446043164</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.3137546468401485</v>
+      </c>
+      <c r="L21" t="n">
         <v>5560</v>
       </c>
-      <c r="G21" t="n">
+      <c r="M21" t="n">
         <v>6950</v>
       </c>
-      <c r="H21" t="n">
+      <c r="N21" t="n">
+        <v>1390</v>
+      </c>
+      <c r="O21" t="n">
+        <v>25</v>
+      </c>
+      <c r="P21" t="n">
+        <v>61.76470588235294</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>65.32352941176471</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>0.4993689381029176</v>
+      </c>
+      <c r="U21" t="n">
+        <v>11.031746</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="W21" t="n">
+        <v>7.115</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.59656</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>30.975</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="AC21" t="n">
         <v>38</v>
-      </c>
-      <c r="I21" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>61.76470588235294</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1390</v>
-      </c>
-      <c r="L21" t="n">
-        <v>25</v>
-      </c>
-      <c r="M21" t="n">
-        <v>65.32352941176471</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>11.031746</v>
-      </c>
-      <c r="P21" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>7.115</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.59656</v>
-      </c>
-      <c r="S21" t="n">
-        <v>47.82608695652174</v>
       </c>
     </row>
     <row r="22">
@@ -1837,49 +2641,87 @@
       <c r="E22" t="n">
         <v>149.5</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>94.25 - 98.96</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>159.08 - 164.00</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>89.53749999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.408026755852831</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.1597665207421302</v>
+      </c>
+      <c r="L22" t="n">
         <v>14098</v>
       </c>
-      <c r="G22" t="n">
+      <c r="M22" t="n">
         <v>29900</v>
       </c>
-      <c r="H22" t="n">
+      <c r="N22" t="n">
+        <v>15802</v>
+      </c>
+      <c r="O22" t="n">
+        <v>112.086820825649</v>
+      </c>
+      <c r="P22" t="n">
+        <v>79.21146953405018</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>69.57885304659499</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>0.6800275011950103</v>
+      </c>
+      <c r="U22" t="n">
+        <v>9.854977</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W22" t="n">
+        <v>11.359999</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>35.71428571428572</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>98.96250000000001</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>159.08</v>
+      </c>
+      <c r="AC22" t="n">
         <v>164</v>
-      </c>
-      <c r="I22" t="n">
-        <v>94.25</v>
-      </c>
-      <c r="J22" t="n">
-        <v>79.21146953405018</v>
-      </c>
-      <c r="K22" t="n">
-        <v>15802</v>
-      </c>
-      <c r="L22" t="n">
-        <v>112.086820825649</v>
-      </c>
-      <c r="M22" t="n">
-        <v>69.57885304659499</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>9.854977</v>
-      </c>
-      <c r="P22" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>11.359999</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="S22" t="n">
-        <v>35.71428571428572</v>
       </c>
     </row>
     <row r="23">
@@ -1902,49 +2744,87 @@
       <c r="E23" t="n">
         <v>29.25</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>24.00 - 25.20</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>31.52 - 32.50</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7.777777777777772</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.3527131782945733</v>
+      </c>
+      <c r="L23" t="n">
         <v>43750</v>
       </c>
-      <c r="G23" t="n">
+      <c r="M23" t="n">
         <v>29250</v>
       </c>
-      <c r="H23" t="n">
+      <c r="N23" t="n">
+        <v>-14500</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-33.14285714285714</v>
+      </c>
+      <c r="P23" t="n">
+        <v>61.76470588235294</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>71.32352941176471</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 25.20</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>0.6347203532967844</v>
+      </c>
+      <c r="U23" t="n">
+        <v>10.227273</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="W23" t="n">
+        <v>6.418</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06801</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>38.46153846153846</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>31.525</v>
+      </c>
+      <c r="AC23" t="n">
         <v>32.5</v>
-      </c>
-      <c r="I23" t="n">
-        <v>24</v>
-      </c>
-      <c r="J23" t="n">
-        <v>61.76470588235294</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-14500</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-33.14285714285714</v>
-      </c>
-      <c r="M23" t="n">
-        <v>71.32352941176471</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>10.227273</v>
-      </c>
-      <c r="P23" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.418</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.06801</v>
-      </c>
-      <c r="S23" t="n">
-        <v>38.46153846153846</v>
       </c>
     </row>
     <row r="24">
@@ -1967,49 +2847,87 @@
       <c r="E24" t="n">
         <v>32.25</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20.80 - 21.84</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>34.92 - 36.00</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8.279069767441866</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2137710168134509</v>
+      </c>
+      <c r="L24" t="n">
         <v>10200</v>
       </c>
-      <c r="G24" t="n">
+      <c r="M24" t="n">
         <v>32250</v>
       </c>
-      <c r="H24" t="n">
+      <c r="N24" t="n">
+        <v>22050</v>
+      </c>
+      <c r="O24" t="n">
+        <v>216.1764705882353</v>
+      </c>
+      <c r="P24" t="n">
+        <v>75.32894736842105</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>75.96710526315789</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>0.4611459049472842</v>
+      </c>
+      <c r="U24" t="n">
+        <v>9.347826</v>
+      </c>
+      <c r="V24" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="W24" t="n">
+        <v>10.986</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>45.15809304913206</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="AC24" t="n">
         <v>36</v>
-      </c>
-      <c r="I24" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>75.32894736842105</v>
-      </c>
-      <c r="K24" t="n">
-        <v>22050</v>
-      </c>
-      <c r="L24" t="n">
-        <v>216.1764705882353</v>
-      </c>
-      <c r="M24" t="n">
-        <v>75.96710526315789</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>9.347826</v>
-      </c>
-      <c r="P24" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>10.986</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>45.15809304913206</v>
       </c>
     </row>
     <row r="25">
@@ -2032,49 +2950,87 @@
       <c r="E25" t="n">
         <v>18.5</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>17.40 - 18.27</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>24.15 - 24.90</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="J25" t="n">
+        <v>30.55675675675675</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.869543147208117</v>
+      </c>
+      <c r="L25" t="n">
         <v>12108</v>
       </c>
-      <c r="G25" t="n">
+      <c r="M25" t="n">
         <v>11100</v>
       </c>
-      <c r="H25" t="n">
+      <c r="N25" t="n">
+        <v>-1008</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-8.325074331020812</v>
+      </c>
+      <c r="P25" t="n">
+        <v>14.66666666666669</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>71.53333333333333</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 18.27</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>0.7667686188704068</v>
+      </c>
+      <c r="U25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="W25" t="n">
+        <v>15.302</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.15896</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>40.00005086250086</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>24.153</v>
+      </c>
+      <c r="AC25" t="n">
         <v>24.9</v>
-      </c>
-      <c r="I25" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>14.66666666666669</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-1008</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-8.325074331020812</v>
-      </c>
-      <c r="M25" t="n">
-        <v>71.53333333333333</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="P25" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>15.302</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.15896</v>
-      </c>
-      <c r="S25" t="n">
-        <v>40.00005086250086</v>
       </c>
     </row>
     <row r="26">
@@ -2097,49 +3053,87 @@
       <c r="E26" t="n">
         <v>5.3</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>4.56 - 4.79</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6.11 - 6.30</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>4.332</v>
+      </c>
+      <c r="J26" t="n">
+        <v>15.30188679245283</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8378099173553719</v>
+      </c>
+      <c r="L26" t="n">
         <v>1528</v>
       </c>
-      <c r="G26" t="n">
+      <c r="M26" t="n">
         <v>1060</v>
       </c>
-      <c r="H26" t="n">
+      <c r="N26" t="n">
+        <v>-468</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-30.6282722513089</v>
+      </c>
+      <c r="P26" t="n">
+        <v>42.52873563218392</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>32.74712643678161</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Reduce/Cut</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Reduce 50%</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>0.4506307483935996</v>
+      </c>
+      <c r="U26" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="W26" t="n">
+        <v>10.2790006</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.03834</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>52.94118307040013</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>4.787999999999999</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.111</v>
+      </c>
+      <c r="AC26" t="n">
         <v>6.3</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="J26" t="n">
-        <v>42.52873563218392</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-468</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-30.6282722513089</v>
-      </c>
-      <c r="M26" t="n">
-        <v>32.74712643678161</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Reduce/Cut</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>10.2790006</v>
-      </c>
-      <c r="R26" t="n">
-        <v>3.03834</v>
-      </c>
-      <c r="S26" t="n">
-        <v>52.94118307040013</v>
       </c>
     </row>
     <row r="27">
@@ -2162,49 +3156,87 @@
       <c r="E27" t="n">
         <v>2.12</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.98 - 2.08</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>4.95 - 5.10</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1.881</v>
+      </c>
+      <c r="J27" t="n">
+        <v>133.3490566037735</v>
+      </c>
+      <c r="K27" t="n">
+        <v>11.82845188284518</v>
+      </c>
+      <c r="L27" t="n">
         <v>4085</v>
       </c>
-      <c r="G27" t="n">
+      <c r="M27" t="n">
         <v>1060</v>
       </c>
-      <c r="H27" t="n">
+      <c r="N27" t="n">
+        <v>-3025</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-74.05140758873929</v>
+      </c>
+      <c r="P27" t="n">
+        <v>4.487179487179492</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>57.05128205128205</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>0.5750221156781765</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-1.854</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.93565</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>44.99999105933206</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.079</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>4.946999999999999</v>
+      </c>
+      <c r="AC27" t="n">
         <v>5.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4.487179487179492</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-3025</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-74.05140758873929</v>
-      </c>
-      <c r="M27" t="n">
-        <v>57.05128205128205</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-1.854</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.93565</v>
-      </c>
-      <c r="S27" t="n">
-        <v>44.99999105933206</v>
       </c>
     </row>
     <row r="28">
@@ -2227,49 +3259,87 @@
       <c r="E28" t="n">
         <v>44.75</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>40.50 - 42.52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>52.87 - 54.50</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>38.475</v>
+      </c>
+      <c r="J28" t="n">
+        <v>18.13407821229051</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.293227091633467</v>
+      </c>
+      <c r="L28" t="n">
         <v>5384</v>
       </c>
-      <c r="G28" t="n">
+      <c r="M28" t="n">
         <v>4475</v>
       </c>
-      <c r="H28" t="n">
+      <c r="N28" t="n">
+        <v>-909</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-16.88335809806836</v>
+      </c>
+      <c r="P28" t="n">
+        <v>30.35714285714285</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>57.96428571428572</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>0.6196314228960125</v>
+      </c>
+      <c r="U28" t="n">
+        <v>14.435484</v>
+      </c>
+      <c r="V28" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="W28" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.33418</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>44.82758620689656</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>42.525</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>52.865</v>
+      </c>
+      <c r="AC28" t="n">
         <v>54.5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="J28" t="n">
-        <v>30.35714285714285</v>
-      </c>
-      <c r="K28" t="n">
-        <v>-909</v>
-      </c>
-      <c r="L28" t="n">
-        <v>-16.88335809806836</v>
-      </c>
-      <c r="M28" t="n">
-        <v>57.96428571428572</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O28" t="n">
-        <v>14.435484</v>
-      </c>
-      <c r="P28" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.33418</v>
-      </c>
-      <c r="S28" t="n">
-        <v>44.82758620689656</v>
       </c>
     </row>
     <row r="29">
@@ -2292,49 +3362,87 @@
       <c r="E29" t="n">
         <v>18.6</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>15.80 - 16.59</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>24.49 - 25.25</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="J29" t="n">
+        <v>31.68010752688171</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.641364902506963</v>
+      </c>
+      <c r="L29" t="n">
         <v>5084</v>
       </c>
-      <c r="G29" t="n">
+      <c r="M29" t="n">
         <v>3720</v>
       </c>
-      <c r="H29" t="n">
+      <c r="N29" t="n">
+        <v>-1364</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-26.82926829268293</v>
+      </c>
+      <c r="P29" t="n">
+        <v>29.62962962962964</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>46.03703703703704</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>0.8269922682385363</v>
+      </c>
+      <c r="U29" t="n">
+        <v>16.607143</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W29" t="n">
+        <v>10.017</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.54054</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>64.62050676638384</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>24.4925</v>
+      </c>
+      <c r="AC29" t="n">
         <v>25.25</v>
-      </c>
-      <c r="I29" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>29.62962962962964</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-1364</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-26.82926829268293</v>
-      </c>
-      <c r="M29" t="n">
-        <v>46.03703703703704</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>16.607143</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>10.017</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.54054</v>
-      </c>
-      <c r="S29" t="n">
-        <v>64.62050676638384</v>
       </c>
     </row>
     <row r="30">
@@ -2357,49 +3465,87 @@
       <c r="E30" t="n">
         <v>3.78</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3.18 - 3.34</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>4.37 - 4.50</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="J30" t="n">
+        <v>15.47619047619049</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.7707509881422931</v>
+      </c>
+      <c r="L30" t="n">
         <v>2896</v>
       </c>
-      <c r="G30" t="n">
+      <c r="M30" t="n">
         <v>1512</v>
       </c>
-      <c r="H30" t="n">
+      <c r="N30" t="n">
+        <v>-1384</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-47.79005524861879</v>
+      </c>
+      <c r="P30" t="n">
+        <v>45.45454545454543</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>44.45454545454545</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Reduce/Cut</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Reduce 50%</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>0.5814084071891462</v>
+      </c>
+      <c r="U30" t="n">
+        <v>12.193548</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.51037</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>51.72413793103448</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.339</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>4.365</v>
+      </c>
+      <c r="AC30" t="n">
         <v>4.5</v>
-      </c>
-      <c r="I30" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="J30" t="n">
-        <v>45.45454545454543</v>
-      </c>
-      <c r="K30" t="n">
-        <v>-1384</v>
-      </c>
-      <c r="L30" t="n">
-        <v>-47.79005524861879</v>
-      </c>
-      <c r="M30" t="n">
-        <v>44.45454545454545</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Reduce/Cut</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>12.193548</v>
-      </c>
-      <c r="P30" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.51037</v>
-      </c>
-      <c r="S30" t="n">
-        <v>51.72413793103448</v>
       </c>
     </row>
   </sheetData>
@@ -2413,7 +3559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2453,51 +3599,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Price_Position</t>
+          <t>Upside_Pct</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ตำแหน่งราคาปัจจุบันเทียบกับรอบ 1 ปี (0 = ต่ำสุด, 100 = สูงสุด)</t>
+          <t>โอกาสกำไร (%) จากราคาปัจจุบันถึงเป้าหมาย</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>&lt; 20 = ราคาอยู่โซนล่าง (น่าสนใจ)</t>
+          <t>&gt; 10% = น่าสนใจสะสม</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>High_52W / Low_52W</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ราคาสูงสุด/ต่ำสุดในรอบ 52 สัปดาห์</t>
+          <t>Risk-Reward Ratio (ความคุ้มค่า)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ใช้ดูแนวรับ-แนวต้านสำคัญ</t>
+          <t>&gt; 2.0 = คุ้มค่าที่จะเสี่ยง</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Advice</t>
+          <t>Target_Action</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>คำแนะนำลงทุน</t>
+          <t>แผนปฏิบัติการระบุราคาและสัดส่วนชัดเจน</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ทำตามระบบ</t>
+          <t>TP = ขายทำกำไร, Reduce = ลดพอร์ต</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Stop_Loss</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>จุดตัดขาดทุนเมื่อหลุดแนวรับ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ห้ามถือหุ้นหากราคาหลุดจุดนี้</t>
         </is>
       </c>
     </row>
